--- a/AAII_Financials/Quarterly/CMCSA_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/CMCSA_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="163" uniqueCount="92">
   <si>
     <t>CMCSA</t>
   </si>
@@ -656,515 +656,527 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AP102"/>
+  <dimension ref="A5:AQ102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="42" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="43" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="43" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="44" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:43" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E7" s="2">
         <v>46112</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>46022</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45930</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45838</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45747</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45657</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45565</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45473</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45382</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45291</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45199</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45107</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>45016</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44926</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44834</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44742</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44651</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44561</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44469</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44377</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44286</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44196</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>44104</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>44012</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43921</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43830</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43738</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43646</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43555</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43465</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>43373</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>43190</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>43100</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AM7" s="2">
         <v>43008</v>
       </c>
-      <c r="AM7" s="2">
+      <c r="AN7" s="2">
         <v>42916</v>
       </c>
-      <c r="AN7" s="2">
+      <c r="AO7" s="2">
         <v>42825</v>
       </c>
-      <c r="AO7" s="2">
+      <c r="AP7" s="2">
         <v>42735</v>
       </c>
-      <c r="AP7" s="2">
+      <c r="AQ7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>29940000</v>
+      </c>
+      <c r="E8" s="3">
         <v>31457000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>32310000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>31198000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>30313000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>29887000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>31914000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>32070000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>29688000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>30058000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>31253000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>30115000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>30513000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>29691000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>30553000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>29849000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>30016000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>31010000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>30336000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>30298000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>28546000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>27205000</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>27708000</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>25532000</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>23715000</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>26609000</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>28398000</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>26827000</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>26858000</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>26859000</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>27846000</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>22135000</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>21735000</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>22791000</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>22075000</v>
       </c>
-      <c r="AL8" s="3">
+      <c r="AM8" s="3">
         <v>21081000</v>
       </c>
-      <c r="AM8" s="3">
+      <c r="AN8" s="3">
         <v>21286000</v>
       </c>
-      <c r="AN8" s="3">
+      <c r="AO8" s="3">
         <v>20587000</v>
       </c>
-      <c r="AO8" s="3">
+      <c r="AP8" s="3">
         <v>21025000</v>
       </c>
-      <c r="AP8" s="3">
+      <c r="AQ8" s="3">
         <v>21319000</v>
       </c>
     </row>
-    <row r="9" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>8389000</v>
+      </c>
+      <c r="E9" s="3">
         <v>10884000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>10305000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>8655000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>7576000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>8415000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>10026000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>10216000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>7961000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>8823000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>10256000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>8652000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>8849000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>9004000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>9807000</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>8949000</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>8887000</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>10570000</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>9880000</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>10395000</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>9256000</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>8919000</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>9438000</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>8565000</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>6817000</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>8301000</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>9300000</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>8316000</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>8255000</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>8569000</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>9252000</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>6711000</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>6300000</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>7429000</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AL9" s="3">
         <v>6905000</v>
       </c>
-      <c r="AL9" s="3">
+      <c r="AM9" s="3">
         <v>6059000</v>
       </c>
-      <c r="AM9" s="3">
+      <c r="AN9" s="3">
         <v>6330000</v>
       </c>
-      <c r="AN9" s="3">
+      <c r="AO9" s="3">
         <v>6061000</v>
       </c>
-      <c r="AO9" s="3">
+      <c r="AP9" s="3">
         <v>6537000</v>
       </c>
-      <c r="AP9" s="3">
+      <c r="AQ9" s="3">
         <v>7003000</v>
       </c>
     </row>
-    <row r="10" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>21551000</v>
+      </c>
+      <c r="E10" s="3">
         <v>20573000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>22005000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>22543000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>22737000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>21472000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>21888000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>21854000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>21727000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>21235000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>20997000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>21463000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>21664000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>20687000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>20746000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>20900000</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>21129000</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>20440000</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>20456000</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>19903000</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>19290000</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>18286000</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>18270000</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>16967000</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>16898000</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>18308000</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>19098000</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>18511000</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>18603000</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>18290000</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>18594000</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>15424000</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>15435000</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>15362000</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AL10" s="3">
         <v>15170000</v>
       </c>
-      <c r="AL10" s="3">
+      <c r="AM10" s="3">
         <v>15022000</v>
       </c>
-      <c r="AM10" s="3">
+      <c r="AN10" s="3">
         <v>14956000</v>
       </c>
-      <c r="AN10" s="3">
+      <c r="AO10" s="3">
         <v>14526000</v>
       </c>
-      <c r="AO10" s="3">
+      <c r="AP10" s="3">
         <v>14488000</v>
       </c>
-      <c r="AP10" s="3">
+      <c r="AQ10" s="3">
         <v>14316000</v>
       </c>
     </row>
-    <row r="11" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1207,8 +1219,9 @@
       <c r="AN11" s="3"/>
       <c r="AO11" s="3"/>
       <c r="AP11" s="3"/>
+      <c r="AQ11" s="3"/>
     </row>
-    <row r="12" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1329,8 +1342,11 @@
       <c r="AP12" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AQ12" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="13" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1451,252 +1467,261 @@
       <c r="AP13" s="3">
         <v>0</v>
       </c>
+      <c r="AQ13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>13000</v>
+      </c>
+      <c r="E14" s="3">
         <v>5000</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>72000</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>60000</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>-9536000</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>24000</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>150000</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>22000</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>89000</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>51000</v>
       </c>
-      <c r="M14" s="3">
-        <v>0</v>
-      </c>
       <c r="N14" s="3">
+        <v>0</v>
+      </c>
+      <c r="O14" s="3">
         <v>87000</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>38000</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>6000</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>-2000</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>8574000</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>-9000</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>33000</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>8000</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>30000</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>36000</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>12000</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>16000</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>10000</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3">
         <v>16000</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AC14" s="3">
         <v>14000</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AD14" s="3">
         <v>12000</v>
       </c>
-      <c r="AD14" s="3">
+      <c r="AE14" s="3">
         <v>33000</v>
       </c>
-      <c r="AE14" s="3">
+      <c r="AF14" s="3">
         <v>84000</v>
       </c>
-      <c r="AF14" s="3">
+      <c r="AG14" s="3">
         <v>51000</v>
       </c>
-      <c r="AG14" s="3">
+      <c r="AH14" s="3">
         <v>125000</v>
       </c>
-      <c r="AH14" s="3">
+      <c r="AI14" s="3">
         <v>-141000</v>
       </c>
-      <c r="AI14" s="3">
+      <c r="AJ14" s="3">
         <v>-200000</v>
       </c>
-      <c r="AJ14" s="3" t="s">
+      <c r="AK14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AK14" s="3">
+      <c r="AL14" s="3">
         <v>20000</v>
       </c>
-      <c r="AL14" s="3">
+      <c r="AM14" s="3">
         <v>-189000</v>
       </c>
-      <c r="AM14" s="3">
+      <c r="AN14" s="3">
         <v>2000</v>
       </c>
-      <c r="AN14" s="3">
+      <c r="AO14" s="3">
         <v>4000</v>
       </c>
-      <c r="AO14" s="3">
+      <c r="AP14" s="3">
         <v>6000</v>
       </c>
-      <c r="AP14" s="3">
+      <c r="AQ14" s="3">
         <v>7000</v>
       </c>
     </row>
-    <row r="15" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>3688000</v>
+      </c>
+      <c r="E15" s="3">
         <v>3866000</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>4188000</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>4019000</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>4154000</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>3849000</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>3832000</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>3878000</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>3540000</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>3551000</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>3528000</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>3493000</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>3538000</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>3777000</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>3472000</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>3333000</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>3468000</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>3548000</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>3582000</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>3478000</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>3383000</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>3362000</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>3252000</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>3320000</v>
-      </c>
-      <c r="AA15" s="3">
-        <v>3264000</v>
       </c>
       <c r="AB15" s="3">
         <v>3264000</v>
       </c>
       <c r="AC15" s="3">
+        <v>3264000</v>
+      </c>
+      <c r="AD15" s="3">
         <v>3177000</v>
       </c>
-      <c r="AD15" s="3">
+      <c r="AE15" s="3">
         <v>3180000</v>
       </c>
-      <c r="AE15" s="3">
+      <c r="AF15" s="3">
         <v>3276000</v>
       </c>
-      <c r="AF15" s="3">
+      <c r="AG15" s="3">
         <v>3320000</v>
       </c>
-      <c r="AG15" s="3">
+      <c r="AH15" s="3">
         <v>3197000</v>
       </c>
-      <c r="AH15" s="3">
+      <c r="AI15" s="3">
         <v>2618000</v>
       </c>
-      <c r="AI15" s="3">
+      <c r="AJ15" s="3">
         <v>2603000</v>
       </c>
-      <c r="AJ15" s="3">
+      <c r="AK15" s="3">
         <v>2599000</v>
       </c>
-      <c r="AK15" s="3">
+      <c r="AL15" s="3">
         <v>2609000</v>
       </c>
-      <c r="AL15" s="3">
+      <c r="AM15" s="3">
         <v>2546000</v>
       </c>
-      <c r="AM15" s="3">
+      <c r="AN15" s="3">
         <v>2507000</v>
       </c>
-      <c r="AN15" s="3">
+      <c r="AO15" s="3">
         <v>2468000</v>
       </c>
-      <c r="AO15" s="3">
+      <c r="AP15" s="3">
         <v>2496000</v>
       </c>
-      <c r="AP15" s="3">
+      <c r="AQ15" s="3">
         <v>2395000</v>
       </c>
     </row>
-    <row r="16" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:43" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1736,252 +1761,259 @@
       <c r="AN16" s="3"/>
       <c r="AO16" s="3"/>
       <c r="AP16" s="3"/>
+      <c r="AQ16" s="3"/>
     </row>
-    <row r="17" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>24780000</v>
+      </c>
+      <c r="E17" s="3">
         <v>27322000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>28824000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>25665000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>24320000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>24228000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>26920000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>26211000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>23053000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>24249000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>26769000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>23640000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>23804000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>24045000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>26023000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>32274000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>23649000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>25441000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>25515000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>24848000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>23039000</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>22166000</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>23790000</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>21456000</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>19068000</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>21757000</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>23151000</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>21487000</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>21502000</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>21677000</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>23332000</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>17299000</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>16721000</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>18146000</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>17946000</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AM17" s="3">
         <v>16302000</v>
       </c>
-      <c r="AM17" s="3">
+      <c r="AN17" s="3">
         <v>16718000</v>
       </c>
-      <c r="AN17" s="3">
+      <c r="AO17" s="3">
         <v>16045000</v>
       </c>
-      <c r="AO17" s="3">
+      <c r="AP17" s="3">
         <v>16767000</v>
       </c>
-      <c r="AP17" s="3">
+      <c r="AQ17" s="3">
         <v>16886000</v>
       </c>
     </row>
-    <row r="18" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>5160000</v>
+      </c>
+      <c r="E18" s="3">
         <v>4135000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>3486000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>5533000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>5993000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>5659000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>4994000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>5859000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>6635000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>5809000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>4484000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>6475000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>6709000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>5646000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>4530000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-2425000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>6367000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>5569000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>4821000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>5450000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>5507000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>5039000</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>3918000</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>4076000</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>4647000</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>4852000</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>5247000</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>5340000</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>5356000</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>5182000</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>4514000</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>4836000</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>5014000</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>4645000</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>4129000</v>
       </c>
-      <c r="AL18" s="3">
+      <c r="AM18" s="3">
         <v>4779000</v>
       </c>
-      <c r="AM18" s="3">
+      <c r="AN18" s="3">
         <v>4568000</v>
       </c>
-      <c r="AN18" s="3">
+      <c r="AO18" s="3">
         <v>4542000</v>
       </c>
-      <c r="AO18" s="3">
+      <c r="AP18" s="3">
         <v>4258000</v>
       </c>
-      <c r="AP18" s="3">
+      <c r="AQ18" s="3">
         <v>4433000</v>
       </c>
     </row>
-    <row r="19" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -2024,618 +2056,634 @@
       <c r="AN19" s="3"/>
       <c r="AO19" s="3"/>
       <c r="AP19" s="3"/>
+      <c r="AQ19" s="3"/>
     </row>
-    <row r="20" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-518000</v>
+      </c>
+      <c r="E20" s="3">
         <v>303000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>128000</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-122000</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-223000</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>93000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>201000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-19000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>344000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-350000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-578000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-137000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-53000</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-613000</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>114000</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-267000</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-897000</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>188000</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>184000</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>766000</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>1216000</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>390000</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>1542000</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-86000</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>420000</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>-716000</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>-73000</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>-110000</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>-55000</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>676000</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>-317000</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>-111000</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>77000</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AK20" s="3">
         <v>126000</v>
       </c>
-      <c r="AK20" s="3">
+      <c r="AL20" s="3">
         <v>122000</v>
       </c>
-      <c r="AL20" s="3">
+      <c r="AM20" s="3">
         <v>70000</v>
       </c>
-      <c r="AM20" s="3">
+      <c r="AN20" s="3">
         <v>99000</v>
       </c>
-      <c r="AN20" s="3">
+      <c r="AO20" s="3">
         <v>130000</v>
       </c>
-      <c r="AO20" s="3">
+      <c r="AP20" s="3">
         <v>234000</v>
       </c>
-      <c r="AP20" s="3">
+      <c r="AQ20" s="3">
         <v>42000</v>
       </c>
     </row>
-    <row r="21" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>9366000</v>
+      </c>
+      <c r="E21" s="3">
         <v>7698000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>7546000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>9674000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>10370000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>9415000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>8625000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>9756000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>9831000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>9710000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>8590000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>10105000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>10300000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>10036000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>8116000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>641000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>8938000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>9305000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>8587000</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>9693000</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>10106000</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>8791000</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>8712000</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>7310000</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>8331000</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>7400000</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>8351000</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>8410000</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>8577000</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>9178000</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>7394000</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>7202000</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>7494000</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>7370000</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>6860000</v>
       </c>
-      <c r="AL21" s="3">
+      <c r="AM21" s="3">
         <v>6953000</v>
       </c>
-      <c r="AM21" s="3">
+      <c r="AN21" s="3">
         <v>7174000</v>
       </c>
-      <c r="AN21" s="3">
+      <c r="AO21" s="3">
         <v>7140000</v>
       </c>
-      <c r="AO21" s="3">
+      <c r="AP21" s="3">
         <v>6988000</v>
       </c>
-      <c r="AP21" s="3">
+      <c r="AQ21" s="3">
         <v>6870000</v>
       </c>
     </row>
-    <row r="22" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>1052000</v>
+      </c>
+      <c r="E22" s="3">
         <v>1094000</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>1126000</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>1128000</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>1105000</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>1050000</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>1069000</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>1037000</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>1026000</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>1002000</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>1019000</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>1060000</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>998000</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>1010000</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>974000</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>960000</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>968000</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>993000</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>1120000</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>1050000</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>1093000</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>1018000</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>1044000</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>1220000</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>1112000</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>1212000</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>1113000</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>1167000</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>1137000</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>1150000</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>1129000</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AI22" s="3">
         <v>830000</v>
       </c>
-      <c r="AI22" s="3">
+      <c r="AJ22" s="3">
         <v>806000</v>
       </c>
-      <c r="AJ22" s="3">
+      <c r="AK22" s="3">
         <v>777000</v>
       </c>
-      <c r="AK22" s="3">
+      <c r="AL22" s="3">
         <v>807000</v>
       </c>
-      <c r="AL22" s="3">
+      <c r="AM22" s="3">
         <v>766000</v>
       </c>
-      <c r="AM22" s="3">
+      <c r="AN22" s="3">
         <v>758000</v>
       </c>
-      <c r="AN22" s="3">
+      <c r="AO22" s="3">
         <v>755000</v>
       </c>
-      <c r="AO22" s="3">
+      <c r="AP22" s="3">
         <v>756000</v>
       </c>
-      <c r="AP22" s="3">
+      <c r="AQ22" s="3">
         <v>751000</v>
       </c>
     </row>
-    <row r="23" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>4613000</v>
+      </c>
+      <c r="E23" s="3">
         <v>2733000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>2160000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>4467000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>14647000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>4492000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>3574000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>4819000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>5176000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>5106000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>4043000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>5465000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>5726000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>5243000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>3670000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-3652000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>4502000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>4764000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>3885000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>5166000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>5630000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>4411000</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>4416000</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>2770000</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>3955000</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>2924000</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>4061000</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>4063000</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>4164000</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>4708000</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>3068000</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>3895000</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>4285000</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>3994000</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>3444000</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AM23" s="3">
         <v>4083000</v>
       </c>
-      <c r="AM23" s="3">
+      <c r="AN23" s="3">
         <v>3909000</v>
       </c>
-      <c r="AN23" s="3">
+      <c r="AO23" s="3">
         <v>3917000</v>
       </c>
-      <c r="AO23" s="3">
+      <c r="AP23" s="3">
         <v>3736000</v>
       </c>
-      <c r="AP23" s="3">
+      <c r="AQ23" s="3">
         <v>3724000</v>
       </c>
     </row>
-    <row r="24" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>1194000</v>
+      </c>
+      <c r="E24" s="3">
         <v>706000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>89000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>1218000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>3603000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>1196000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>-1110000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>1243000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>1336000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>1328000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>890000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>1468000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>1537000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>1476000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>797000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>1014000</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>1261000</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>1288000</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>905000</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>1235000</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>2000000</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>1119000</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>979000</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>739000</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>946000</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>700000</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>861000</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>775000</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>961000</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>1076000</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>486000</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>851000</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>1077000</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>946000</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>1075000</v>
       </c>
-      <c r="AL24" s="3">
+      <c r="AM24" s="3">
         <v>1409000</v>
       </c>
-      <c r="AM24" s="3">
+      <c r="AN24" s="3">
         <v>1367000</v>
       </c>
-      <c r="AN24" s="3">
+      <c r="AO24" s="3">
         <v>1262000</v>
       </c>
-      <c r="AO24" s="3">
+      <c r="AP24" s="3">
         <v>1319000</v>
       </c>
-      <c r="AP24" s="3">
+      <c r="AQ24" s="3">
         <v>1400000</v>
       </c>
     </row>
-    <row r="25" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2756,252 +2804,261 @@
       <c r="AP25" s="3">
         <v>0</v>
       </c>
+      <c r="AQ25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>3419000</v>
+      </c>
+      <c r="E26" s="3">
         <v>2027000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>2071000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>3249000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>11044000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>3296000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>4684000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>3576000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>3840000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>3778000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>3153000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>3997000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>4189000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>3767000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>2873000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-4666000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>3241000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>3476000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>2980000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>3931000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>3630000</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>3292000</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>3437000</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>2031000</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>3009000</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>2224000</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>3200000</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>3288000</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>3203000</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>3632000</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>2582000</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>3044000</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>3208000</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>3048000</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>2369000</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AM26" s="3">
         <v>2674000</v>
       </c>
-      <c r="AM26" s="3">
+      <c r="AN26" s="3">
         <v>2542000</v>
       </c>
-      <c r="AN26" s="3">
+      <c r="AO26" s="3">
         <v>2655000</v>
       </c>
-      <c r="AO26" s="3">
+      <c r="AP26" s="3">
         <v>2417000</v>
       </c>
-      <c r="AP26" s="3">
+      <c r="AQ26" s="3">
         <v>2324000</v>
       </c>
     </row>
-    <row r="27" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>3526000</v>
+      </c>
+      <c r="E27" s="3">
         <v>2174000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>2168000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>3332000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>11123000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>3375000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>4777000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>3629000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>3929000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>3857000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>3260000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>4046000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>4248000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>3834000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>3023000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-4598000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>3396000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>3549000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>3057000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>4035000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>3738000</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>3329000</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>3380000</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>2019000</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>2988000</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>2147000</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>3162000</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>3217000</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>3125000</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>3553000</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>2511000</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>3034000</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>3216000</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>2990000</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>2317000</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AM27" s="3">
         <v>2642000</v>
       </c>
-      <c r="AM27" s="3">
+      <c r="AN27" s="3">
         <v>2521000</v>
       </c>
-      <c r="AN27" s="3">
+      <c r="AO27" s="3">
         <v>2573000</v>
       </c>
-      <c r="AO27" s="3">
+      <c r="AP27" s="3">
         <v>2296000</v>
       </c>
-      <c r="AP27" s="3">
+      <c r="AQ27" s="3">
         <v>2237000</v>
       </c>
     </row>
-    <row r="28" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -3122,8 +3179,11 @@
       <c r="AP28" s="3">
         <v>0</v>
       </c>
+      <c r="AQ28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -3199,8 +3259,8 @@
       <c r="AA29" s="3">
         <v>0</v>
       </c>
-      <c r="AB29" s="3" t="s">
-        <v>8</v>
+      <c r="AB29" s="3">
+        <v>0</v>
       </c>
       <c r="AC29" s="3" t="s">
         <v>8</v>
@@ -3214,23 +3274,23 @@
       <c r="AF29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AG29" s="3">
-        <v>0</v>
+      <c r="AG29" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AH29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI29" s="3">
         <v>-148000</v>
       </c>
-      <c r="AI29" s="3">
-        <v>0</v>
-      </c>
       <c r="AJ29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK29" s="3">
         <v>128000</v>
       </c>
-      <c r="AK29" s="3">
+      <c r="AL29" s="3">
         <v>12682000</v>
-      </c>
-      <c r="AL29" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AM29" s="3" t="s">
         <v>8</v>
@@ -3244,8 +3304,11 @@
       <c r="AP29" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AQ29" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="30" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3366,8 +3429,11 @@
       <c r="AP30" s="3">
         <v>0</v>
       </c>
+      <c r="AQ30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3488,252 +3554,261 @@
       <c r="AP31" s="3">
         <v>0</v>
       </c>
+      <c r="AQ31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>518000</v>
+      </c>
+      <c r="E32" s="3">
         <v>-303000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-128000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>122000</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>223000</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-93000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-201000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>19000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-344000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>350000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>578000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>137000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>53000</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>613000</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-114000</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>267000</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>897000</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-188000</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-184000</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-766000</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-1216000</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-390000</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-1542000</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>86000</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-420000</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>716000</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>73000</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>110000</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>55000</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>-676000</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>317000</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>111000</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>-77000</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AK32" s="3">
         <v>-126000</v>
       </c>
-      <c r="AK32" s="3">
+      <c r="AL32" s="3">
         <v>-122000</v>
       </c>
-      <c r="AL32" s="3">
+      <c r="AM32" s="3">
         <v>-70000</v>
       </c>
-      <c r="AM32" s="3">
+      <c r="AN32" s="3">
         <v>-99000</v>
       </c>
-      <c r="AN32" s="3">
+      <c r="AO32" s="3">
         <v>-130000</v>
       </c>
-      <c r="AO32" s="3">
+      <c r="AP32" s="3">
         <v>-234000</v>
       </c>
-      <c r="AP32" s="3">
+      <c r="AQ32" s="3">
         <v>-42000</v>
       </c>
     </row>
-    <row r="33" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>3526000</v>
+      </c>
+      <c r="E33" s="3">
         <v>2174000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>2168000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>3332000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>11123000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>3375000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>4777000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>3629000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>3929000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>3857000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>3260000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>4046000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>4248000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>3834000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>3023000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-4598000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>3396000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>3549000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>3057000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>4035000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>3738000</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>3329000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>3380000</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>2019000</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>2988000</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>2147000</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>3162000</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>3217000</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>3125000</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>3553000</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>2511000</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>2886000</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>3216000</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>3118000</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>14999000</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AM33" s="3">
         <v>2642000</v>
       </c>
-      <c r="AM33" s="3">
+      <c r="AN33" s="3">
         <v>2521000</v>
       </c>
-      <c r="AN33" s="3">
+      <c r="AO33" s="3">
         <v>2573000</v>
       </c>
-      <c r="AO33" s="3">
+      <c r="AP33" s="3">
         <v>2296000</v>
       </c>
-      <c r="AP33" s="3">
+      <c r="AQ33" s="3">
         <v>2237000</v>
       </c>
     </row>
-    <row r="34" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3854,257 +3929,266 @@
       <c r="AP34" s="3">
         <v>0</v>
       </c>
+      <c r="AQ34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>3526000</v>
+      </c>
+      <c r="E35" s="3">
         <v>2174000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>2168000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>3332000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>11123000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>3375000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>4777000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>3629000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>3929000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>3857000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>3260000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>4046000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>4248000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>3834000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>3023000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-4598000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>3396000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>3549000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>3057000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>4035000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>3738000</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>3329000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>3380000</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>2019000</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>2988000</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>2147000</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>3162000</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>3217000</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>3125000</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>3553000</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>2511000</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>2886000</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>3216000</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>3118000</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>14999000</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AM35" s="3">
         <v>2642000</v>
       </c>
-      <c r="AM35" s="3">
+      <c r="AN35" s="3">
         <v>2521000</v>
       </c>
-      <c r="AN35" s="3">
+      <c r="AO35" s="3">
         <v>2573000</v>
       </c>
-      <c r="AO35" s="3">
+      <c r="AP35" s="3">
         <v>2296000</v>
       </c>
-      <c r="AP35" s="3">
+      <c r="AQ35" s="3">
         <v>2237000</v>
       </c>
     </row>
-    <row r="37" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:43" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E38" s="2">
         <v>46112</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>46022</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45930</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45838</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45747</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45657</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45565</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45473</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45382</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45291</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45199</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45107</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>45016</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44926</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44834</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44742</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44651</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44561</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44469</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44377</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44286</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44196</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>44104</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>44012</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43921</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43830</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43738</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43646</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43555</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43465</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>43373</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>43190</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>43100</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AM38" s="2">
         <v>43008</v>
       </c>
-      <c r="AM38" s="2">
+      <c r="AN38" s="2">
         <v>42916</v>
       </c>
-      <c r="AN38" s="2">
+      <c r="AO38" s="2">
         <v>42825</v>
       </c>
-      <c r="AO38" s="2">
+      <c r="AP38" s="2">
         <v>42735</v>
       </c>
-      <c r="AP38" s="2">
+      <c r="AQ38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -4147,8 +4231,9 @@
       <c r="AN39" s="3"/>
       <c r="AO39" s="3"/>
       <c r="AP39" s="3"/>
+      <c r="AQ39" s="3"/>
     </row>
-    <row r="40" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -4191,130 +4276,134 @@
       <c r="AN40" s="3"/>
       <c r="AO40" s="3"/>
       <c r="AP40" s="3"/>
+      <c r="AQ40" s="3"/>
     </row>
-    <row r="41" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>7661000</v>
+      </c>
+      <c r="E41" s="3">
         <v>9468000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>9481000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>9325000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>9687000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>8593000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>7322000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>8814000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>6065000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>6515000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>6215000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>6435000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>7146000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>5535000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>4749000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>5695000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>6822000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>8880000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>8711000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>11806000</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>12378000</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>14950000</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>11740000</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>13707000</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>13935000</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>8516000</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>5500000</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>3507000</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>3919000</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>3498000</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>3814000</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>10616000</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>5726000</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>6030000</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>3428000</v>
       </c>
-      <c r="AL41" s="3">
+      <c r="AM41" s="3">
         <v>4114000</v>
       </c>
-      <c r="AM41" s="3">
+      <c r="AN41" s="3">
         <v>2693000</v>
       </c>
-      <c r="AN41" s="3">
+      <c r="AO41" s="3">
         <v>4022000</v>
       </c>
-      <c r="AO41" s="3">
+      <c r="AP41" s="3">
         <v>3301000</v>
       </c>
-      <c r="AP41" s="3">
+      <c r="AQ41" s="3">
         <v>2807000</v>
       </c>
     </row>
-    <row r="42" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -4435,130 +4524,136 @@
       <c r="AP42" s="3">
         <v>0</v>
       </c>
+      <c r="AQ42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>13955000</v>
+      </c>
+      <c r="E43" s="3">
         <v>14078000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>13869000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>13214000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>13040000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>12881000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>15661000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>14036000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>13167000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>13144000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>13813000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>12835000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>12980000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>12287000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>12672000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>11918000</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>11956000</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>12300000</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>12008000</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>11974000</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>11110000</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>10986000</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>11466000</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>10310000</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>10227000</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>10800000</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>11292000</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>10684000</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>10835000</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>10736000</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>11104000</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>8983000</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>8847000</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>8759000</v>
       </c>
-      <c r="AK43" s="3">
+      <c r="AL43" s="3">
         <v>8415000</v>
       </c>
-      <c r="AL43" s="3">
+      <c r="AM43" s="3">
         <v>7915000</v>
       </c>
-      <c r="AM43" s="3">
+      <c r="AN43" s="3">
         <v>7849000</v>
       </c>
-      <c r="AN43" s="3">
+      <c r="AO43" s="3">
         <v>7525000</v>
       </c>
-      <c r="AO43" s="3">
+      <c r="AP43" s="3">
         <v>7955000</v>
       </c>
-      <c r="AP43" s="3">
+      <c r="AQ43" s="3">
         <v>7533000</v>
       </c>
     </row>
-    <row r="44" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -4601,8 +4696,8 @@
       <c r="P44" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q44" s="3">
-        <v>0</v>
+      <c r="Q44" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="R44" s="3">
         <v>0</v>
@@ -4679,618 +4774,636 @@
       <c r="AP44" s="3">
         <v>0</v>
       </c>
+      <c r="AQ44" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="45" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>4719000</v>
+      </c>
+      <c r="E45" s="3">
         <v>5276000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>6217000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>6318000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>6309000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>5840000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>3818000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>4336000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>4220000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>4319000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>3959000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>4818000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>4741000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>4513000</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>4405000</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>5803000</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>5414000</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>4201000</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>4088000</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>3647000</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>3558000</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>3502000</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>3535000</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>3352000</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>3323000</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>4768000</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>8600000</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>8132000</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>6607000</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>6039000</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>6930000</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>3607000</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>3642000</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AK45" s="3">
         <v>3964000</v>
       </c>
-      <c r="AK45" s="3">
+      <c r="AL45" s="3">
         <v>4090000</v>
       </c>
-      <c r="AL45" s="3">
+      <c r="AM45" s="3">
         <v>3931000</v>
       </c>
-      <c r="AM45" s="3">
+      <c r="AN45" s="3">
         <v>4290000</v>
       </c>
-      <c r="AN45" s="3">
+      <c r="AO45" s="3">
         <v>3698000</v>
       </c>
-      <c r="AO45" s="3">
+      <c r="AP45" s="3">
         <v>5105000</v>
       </c>
-      <c r="AP45" s="3">
+      <c r="AQ45" s="3">
         <v>4888000</v>
       </c>
     </row>
-    <row r="46" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>26335000</v>
+      </c>
+      <c r="E46" s="3">
         <v>28822000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>29567000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>28857000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>29036000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>27314000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>26801000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>27186000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>23452000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>23978000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>23987000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>24141000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>24922000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>22377000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>21826000</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>23416000</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>24192000</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>25381000</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>24807000</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>27427000</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>27046000</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>29438000</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>26741000</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>27369000</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>27485000</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>24084000</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>25392000</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>22323000</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>21361000</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>20273000</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>21848000</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>23206000</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>18215000</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AK46" s="3">
         <v>18753000</v>
       </c>
-      <c r="AK46" s="3">
+      <c r="AL46" s="3">
         <v>16343000</v>
       </c>
-      <c r="AL46" s="3">
+      <c r="AM46" s="3">
         <v>15960000</v>
       </c>
-      <c r="AM46" s="3">
+      <c r="AN46" s="3">
         <v>14832000</v>
       </c>
-      <c r="AN46" s="3">
+      <c r="AO46" s="3">
         <v>15245000</v>
       </c>
-      <c r="AO46" s="3">
+      <c r="AP46" s="3">
         <v>16361000</v>
       </c>
-      <c r="AP46" s="3">
+      <c r="AQ46" s="3">
         <v>15228000</v>
       </c>
     </row>
-    <row r="47" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>7828000</v>
+      </c>
+      <c r="E47" s="3">
         <v>7450000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>7952000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>8324000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>8463000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>8524000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>8647000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>9021000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>9171000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>9548000</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>8522000</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>8041000</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>7761000</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>7834000</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>9627000</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>9607000</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>9975000</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>10708000</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>10319000</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>10750000</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>10558000</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>9437000</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>9358000</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>8269000</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>8596000</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>8403000</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>9020000</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>9550000</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>9744000</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>10344000</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>9282000</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AI47" s="3">
         <v>8931000</v>
       </c>
-      <c r="AI47" s="3">
+      <c r="AJ47" s="3">
         <v>8629000</v>
       </c>
-      <c r="AJ47" s="3">
+      <c r="AK47" s="3">
         <v>7095000</v>
       </c>
-      <c r="AK47" s="3">
+      <c r="AL47" s="3">
         <v>6931000</v>
       </c>
-      <c r="AL47" s="3">
+      <c r="AM47" s="3">
         <v>6695000</v>
       </c>
-      <c r="AM47" s="3">
+      <c r="AN47" s="3">
         <v>6521000</v>
       </c>
-      <c r="AN47" s="3">
+      <c r="AO47" s="3">
         <v>5938000</v>
       </c>
-      <c r="AO47" s="3">
+      <c r="AP47" s="3">
         <v>5247000</v>
       </c>
-      <c r="AP47" s="3">
+      <c r="AQ47" s="3">
         <v>3857000</v>
       </c>
     </row>
-    <row r="48" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>66127000</v>
+      </c>
+      <c r="E48" s="3">
         <v>65472000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>70967000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>64773000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>64025000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>63292000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>68072000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>61775000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>60507000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>59918000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>65472000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>58165000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>56851000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>56279000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>55485000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>53555000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>53508000</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>53820000</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>54047000</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>52809000</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>52769000</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>52317000</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>51995000</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>50466000</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>48985000</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>48442000</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>52360000</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>48379000</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>47638000</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>49821000</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>44437000</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>39855000</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>39355000</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>39068000</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AL48" s="3">
         <v>38470000</v>
       </c>
-      <c r="AL48" s="3">
+      <c r="AM48" s="3">
         <v>37856000</v>
       </c>
-      <c r="AM48" s="3">
+      <c r="AN48" s="3">
         <v>37171000</v>
       </c>
-      <c r="AN48" s="3">
+      <c r="AO48" s="3">
         <v>36626000</v>
       </c>
-      <c r="AO48" s="3">
+      <c r="AP48" s="3">
         <v>36253000</v>
       </c>
-      <c r="AP48" s="3">
+      <c r="AQ48" s="3">
         <v>35656000</v>
       </c>
     </row>
-    <row r="49" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>132122000</v>
+      </c>
+      <c r="E49" s="3">
         <v>133157000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>143341000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>144150000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>145789000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>143402000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>143173000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>145864000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>144104000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>145096000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>146500000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>145304000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>147168000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>147329000</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>159727000</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>157068000</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>168201000</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>173245000</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>175940000</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>175029000</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>176487000</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>177315000</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>178763000</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>175489000</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>173118000</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>173640000</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>173151000</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>170089000</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>171939000</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>172391000</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>171714000</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>122094000</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>122496000</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AK49" s="3">
         <v>122253000</v>
       </c>
-      <c r="AK49" s="3">
+      <c r="AL49" s="3">
         <v>121364000</v>
       </c>
-      <c r="AL49" s="3">
+      <c r="AM49" s="3">
         <v>121645000</v>
       </c>
-      <c r="AM49" s="3">
+      <c r="AN49" s="3">
         <v>121608000</v>
       </c>
-      <c r="AN49" s="3">
+      <c r="AO49" s="3">
         <v>121938000</v>
       </c>
-      <c r="AO49" s="3">
+      <c r="AP49" s="3">
         <v>119870000</v>
       </c>
-      <c r="AP49" s="3">
+      <c r="AQ49" s="3">
         <v>120525000</v>
       </c>
     </row>
-    <row r="50" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -5411,8 +5524,11 @@
       <c r="AP50" s="3">
         <v>0</v>
       </c>
+      <c r="AQ50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5533,130 +5649,136 @@
       <c r="AP51" s="3">
         <v>0</v>
       </c>
+      <c r="AQ51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>23642000</v>
+      </c>
+      <c r="E52" s="3">
         <v>23667000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>18059000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>25675000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>25299000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>24027000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>17109000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>24826000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>24160000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>23860000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>18019000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>24794000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>25445000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>25610000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>10610000</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>10662000</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>11156000</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>10920000</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>10792000</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>11046000</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>10144000</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>10004000</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>7012000</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>7347000</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>7794000</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>7852000</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>3491000</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>6033000</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>5873000</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>3360000</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>4403000</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>6549000</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>2553000</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3">
         <v>3707000</v>
       </c>
-      <c r="AK52" s="3">
+      <c r="AL52" s="3">
         <v>4354000</v>
       </c>
-      <c r="AL52" s="3">
+      <c r="AM52" s="3">
         <v>3145000</v>
       </c>
-      <c r="AM52" s="3">
+      <c r="AN52" s="3">
         <v>2899000</v>
       </c>
-      <c r="AN52" s="3">
+      <c r="AO52" s="3">
         <v>2732000</v>
       </c>
-      <c r="AO52" s="3">
+      <c r="AP52" s="3">
         <v>2769000</v>
       </c>
-      <c r="AP52" s="3">
+      <c r="AQ52" s="3">
         <v>2658000</v>
       </c>
     </row>
-    <row r="53" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5777,130 +5899,136 @@
       <c r="AP53" s="3">
         <v>0</v>
       </c>
+      <c r="AQ53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>257548000</v>
+      </c>
+      <c r="E54" s="3">
         <v>260002000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>272631000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>272995000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>273850000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>267770000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>266211000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>269871000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>262555000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>263601000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>264811000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>261072000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>262147000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>259429000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>257275000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>254308000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>267032000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>274074000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>275905000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>277061000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>277004000</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>278511000</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>273869000</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>268940000</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>265978000</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>262421000</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>263414000</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>256374000</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>256555000</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>256189000</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>251684000</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>200635000</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>191248000</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>190876000</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>187462000</v>
       </c>
-      <c r="AL54" s="3">
+      <c r="AM54" s="3">
         <v>185301000</v>
       </c>
-      <c r="AM54" s="3">
+      <c r="AN54" s="3">
         <v>183031000</v>
       </c>
-      <c r="AN54" s="3">
+      <c r="AO54" s="3">
         <v>182479000</v>
       </c>
-      <c r="AO54" s="3">
+      <c r="AP54" s="3">
         <v>180500000</v>
       </c>
-      <c r="AP54" s="3">
+      <c r="AQ54" s="3">
         <v>177924000</v>
       </c>
     </row>
-    <row r="55" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5943,8 +6071,9 @@
       <c r="AN55" s="3"/>
       <c r="AO55" s="3"/>
       <c r="AP55" s="3"/>
+      <c r="AQ55" s="3"/>
     </row>
-    <row r="56" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5987,740 +6116,759 @@
       <c r="AN56" s="3"/>
       <c r="AO56" s="3"/>
       <c r="AP56" s="3"/>
+      <c r="AQ56" s="3"/>
     </row>
-    <row r="57" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>11864000</v>
+      </c>
+      <c r="E57" s="3">
         <v>11977000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>11058000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>11689000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>11826000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>11545000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>11321000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>11779000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>11736000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>11792000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>12437000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>12214000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>12213000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>12159000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>12544000</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>12241000</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>12304000</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>12707000</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>12455000</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>12020000</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>11672000</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>11148000</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>11364000</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>10979000</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>10426000</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>9963000</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>10826000</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>10198000</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>10014000</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>10232000</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>8494000</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>7036000</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>6940000</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>7349000</v>
       </c>
-      <c r="AK57" s="3">
+      <c r="AL57" s="3">
         <v>6908000</v>
       </c>
-      <c r="AL57" s="3">
+      <c r="AM57" s="3">
         <v>6976000</v>
       </c>
-      <c r="AM57" s="3">
+      <c r="AN57" s="3">
         <v>6730000</v>
       </c>
-      <c r="AN57" s="3">
+      <c r="AO57" s="3">
         <v>6658000</v>
       </c>
-      <c r="AO57" s="3">
+      <c r="AP57" s="3">
         <v>6915000</v>
       </c>
-      <c r="AP57" s="3">
+      <c r="AQ57" s="3">
         <v>6594000</v>
       </c>
     </row>
-    <row r="58" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>6117000</v>
+      </c>
+      <c r="E58" s="3">
         <v>5394000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>6644000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>5852000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>5720000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>6848000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>5658000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>2610000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>1021000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>2502000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>2817000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>8152000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>7697000</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>6303000</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>1743000</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>2047000</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>2083000</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>2117000</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>2132000</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>695000</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>3407000</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>4777000</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>3146000</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>4429000</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>4046000</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>2973000</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>4452000</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>1039000</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>6365000</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>4629000</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>4398000</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AI58" s="3">
         <v>3173000</v>
       </c>
-      <c r="AI58" s="3">
+      <c r="AJ58" s="3">
         <v>2634000</v>
       </c>
-      <c r="AJ58" s="3">
+      <c r="AK58" s="3">
         <v>3039000</v>
       </c>
-      <c r="AK58" s="3">
+      <c r="AL58" s="3">
         <v>5134000</v>
       </c>
-      <c r="AL58" s="3">
+      <c r="AM58" s="3">
         <v>5241000</v>
       </c>
-      <c r="AM58" s="3">
+      <c r="AN58" s="3">
         <v>6358000</v>
       </c>
-      <c r="AN58" s="3">
+      <c r="AO58" s="3">
         <v>3509000</v>
       </c>
-      <c r="AO58" s="3">
+      <c r="AP58" s="3">
         <v>5480000</v>
       </c>
-      <c r="AP58" s="3">
+      <c r="AQ58" s="3">
         <v>3333000</v>
       </c>
     </row>
-    <row r="59" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>3787000</v>
+      </c>
+      <c r="E59" s="3">
         <v>4789000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>4098000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>4219000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>4031000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>12932000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>12674000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>14420000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>14630000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>14196000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>12408000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>5219000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>5139000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>4305000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>13600000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>13711000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>13198000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>14833000</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>14761000</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>14023000</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>14235000</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>14886000</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>14286000</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>14103000</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>13973000</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>14664000</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>15014000</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>14752000</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>14629000</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>13056000</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>14711000</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>9418000</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>9433000</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>8791000</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AL59" s="3">
         <v>9951000</v>
       </c>
-      <c r="AL59" s="3">
+      <c r="AM59" s="3">
         <v>9232000</v>
       </c>
-      <c r="AM59" s="3">
+      <c r="AN59" s="3">
         <v>9188000</v>
       </c>
-      <c r="AN59" s="3">
+      <c r="AO59" s="3">
         <v>8907000</v>
       </c>
-      <c r="AO59" s="3">
+      <c r="AP59" s="3">
         <v>9140000</v>
       </c>
-      <c r="AP59" s="3">
+      <c r="AQ59" s="3">
         <v>8111000</v>
       </c>
     </row>
-    <row r="60" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>33093000</v>
+      </c>
+      <c r="E60" s="3">
         <v>33308000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>33524000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>32702000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>31792000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>42325000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>39581000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>37786000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>35342000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>40324000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>40198000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>34468000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>32925000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>32415000</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>27887000</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>27999000</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>27585000</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>29657000</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>29348000</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>26738000</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>29314000</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>30811000</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>28796000</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>29511000</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>28445000</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>27600000</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>30292000</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>25989000</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>31008000</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>27917000</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>27603000</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>19627000</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>19007000</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AK60" s="3">
         <v>19179000</v>
       </c>
-      <c r="AK60" s="3">
+      <c r="AL60" s="3">
         <v>21993000</v>
       </c>
-      <c r="AL60" s="3">
+      <c r="AM60" s="3">
         <v>21449000</v>
       </c>
-      <c r="AM60" s="3">
+      <c r="AN60" s="3">
         <v>22276000</v>
       </c>
-      <c r="AN60" s="3">
+      <c r="AO60" s="3">
         <v>19074000</v>
       </c>
-      <c r="AO60" s="3">
+      <c r="AP60" s="3">
         <v>21535000</v>
       </c>
-      <c r="AP60" s="3">
+      <c r="AQ60" s="3">
         <v>18038000</v>
       </c>
     </row>
-    <row r="61" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>84264000</v>
+      </c>
+      <c r="E61" s="3">
         <v>89218000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>98389000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>93211000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>95808000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>92274000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>99755000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>98754000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>97107000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>94071000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>100859000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>94351000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>94972000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>94403000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>98240000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>95576000</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>96630000</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>97614000</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>97888000</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>101691000</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>100344000</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>104104000</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>105782000</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>105162000</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>105931000</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>105770000</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>102931000</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>105012000</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>101248000</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>104464000</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>107345000</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>69711000</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>61946000</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>63678000</v>
       </c>
-      <c r="AK61" s="3">
+      <c r="AL61" s="3">
         <v>59422000</v>
       </c>
-      <c r="AL61" s="3">
+      <c r="AM61" s="3">
         <v>59720000</v>
       </c>
-      <c r="AM61" s="3">
+      <c r="AN61" s="3">
         <v>57210000</v>
       </c>
-      <c r="AN61" s="3">
+      <c r="AO61" s="3">
         <v>58276000</v>
       </c>
-      <c r="AO61" s="3">
+      <c r="AP61" s="3">
         <v>55566000</v>
       </c>
-      <c r="AP61" s="3">
+      <c r="AQ61" s="3">
         <v>57095000</v>
       </c>
     </row>
-    <row r="62" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>20641000</v>
+      </c>
+      <c r="E62" s="3">
         <v>20049000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>14933000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>20365000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>20381000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>20071000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>14709000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>19876000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>19211000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>19314000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>13666000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>19141000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>19500000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>19548000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>49110000</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>49391000</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>49746000</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>50298000</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>50660000</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>50806000</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>50300000</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>48950000</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>46273000</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>45442000</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>45555000</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>45009000</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>44945000</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>44845000</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>45140000</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>46630000</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>42918000</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>37635000</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>37209000</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3">
         <v>35955000</v>
       </c>
-      <c r="AK62" s="3">
+      <c r="AL62" s="3">
         <v>35231000</v>
       </c>
-      <c r="AL62" s="3">
+      <c r="AM62" s="3">
         <v>46516000</v>
       </c>
-      <c r="AM62" s="3">
+      <c r="AN62" s="3">
         <v>46246000</v>
       </c>
-      <c r="AN62" s="3">
+      <c r="AO62" s="3">
         <v>46025000</v>
       </c>
-      <c r="AO62" s="3">
+      <c r="AP62" s="3">
         <v>45779000</v>
       </c>
-      <c r="AP62" s="3">
+      <c r="AQ62" s="3">
         <v>45642000</v>
       </c>
     </row>
-    <row r="63" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6841,8 +6989,11 @@
       <c r="AP63" s="3">
         <v>0</v>
       </c>
+      <c r="AQ63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6963,8 +7114,11 @@
       <c r="AP64" s="3">
         <v>0</v>
       </c>
+      <c r="AQ64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -7085,130 +7239,136 @@
       <c r="AP65" s="3">
         <v>0</v>
       </c>
+      <c r="AQ65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>167593000</v>
+      </c>
+      <c r="E66" s="3">
         <v>171462000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>175255000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>175359000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>176392000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>180470000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>179937000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>183329000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>178615000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>180309000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>181344000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>177679000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>177230000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>175974000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>176332000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>174012000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>175606000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>179382000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>179813000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>181279000</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>182069000</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>185936000</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>183546000</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>182764000</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>182364000</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>180915000</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>180688000</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>178230000</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>179705000</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>181230000</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>180071000</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>129112000</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>120554000</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>121394000</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>118846000</v>
       </c>
-      <c r="AL66" s="3">
+      <c r="AM66" s="3">
         <v>129874000</v>
       </c>
-      <c r="AM66" s="3">
+      <c r="AN66" s="3">
         <v>128026000</v>
       </c>
-      <c r="AN66" s="3">
+      <c r="AO66" s="3">
         <v>127420000</v>
       </c>
-      <c r="AO66" s="3">
+      <c r="AP66" s="3">
         <v>126557000</v>
       </c>
-      <c r="AP66" s="3">
+      <c r="AQ66" s="3">
         <v>124443000</v>
       </c>
     </row>
-    <row r="67" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -7251,8 +7411,9 @@
       <c r="AN67" s="3"/>
       <c r="AO67" s="3"/>
       <c r="AP67" s="3"/>
+      <c r="AQ67" s="3"/>
     </row>
-    <row r="68" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -7373,8 +7534,11 @@
       <c r="AP68" s="3">
         <v>0</v>
       </c>
+      <c r="AQ68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -7495,8 +7659,11 @@
       <c r="AP69" s="3">
         <v>0</v>
       </c>
+      <c r="AQ69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -7617,8 +7784,11 @@
       <c r="AP70" s="3">
         <v>0</v>
       </c>
+      <c r="AQ70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7739,130 +7909,136 @@
       <c r="AP71" s="3">
         <v>0</v>
       </c>
+      <c r="AQ71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>60298000</v>
+      </c>
+      <c r="E72" s="3">
         <v>58602000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>66675000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>66875000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>66000000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>57473000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>56972000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>55105000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>54308000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>53425000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>52892000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>53751000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>53900000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>52524000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>51609000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>52541000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>61209000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>61555000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>61902000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>61783000</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>60359000</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>58321000</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>56438000</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>54254000</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>53420000</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>51516000</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>50695000</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>48570000</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>46425000</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>44379000</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>41983000</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>41218000</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>40269000</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>38961000</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>38202000</v>
       </c>
-      <c r="AL72" s="3">
+      <c r="AM72" s="3">
         <v>24979000</v>
       </c>
-      <c r="AM72" s="3">
+      <c r="AN72" s="3">
         <v>24560000</v>
       </c>
-      <c r="AN72" s="3">
+      <c r="AO72" s="3">
         <v>24063000</v>
       </c>
-      <c r="AO72" s="3">
+      <c r="AP72" s="3">
         <v>23076000</v>
       </c>
-      <c r="AP72" s="3">
+      <c r="AQ72" s="3">
         <v>22510000</v>
       </c>
     </row>
-    <row r="73" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7983,8 +8159,11 @@
       <c r="AP73" s="3">
         <v>0</v>
       </c>
+      <c r="AQ73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -8105,8 +8284,11 @@
       <c r="AP74" s="3">
         <v>0</v>
       </c>
+      <c r="AQ74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -8227,130 +8409,136 @@
       <c r="AP75" s="3">
         <v>0</v>
       </c>
+      <c r="AQ75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>89763000</v>
+      </c>
+      <c r="E76" s="3">
         <v>88274000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>96903000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>97081000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>96851000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>86638000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>85560000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>85774000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>83219000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>82549000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>82703000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>82625000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>84119000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>82421000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>80943000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>80296000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>91426000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>94692000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>96092000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>95782000</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>94935000</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>92575000</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>90323000</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>86176000</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>83614000</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>81506000</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>82726000</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>78144000</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>76850000</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>74959000</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>71613000</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>71523000</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>70694000</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>69482000</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>68616000</v>
       </c>
-      <c r="AL76" s="3">
+      <c r="AM76" s="3">
         <v>55427000</v>
       </c>
-      <c r="AM76" s="3">
+      <c r="AN76" s="3">
         <v>55005000</v>
       </c>
-      <c r="AN76" s="3">
+      <c r="AO76" s="3">
         <v>55059000</v>
       </c>
-      <c r="AO76" s="3">
+      <c r="AP76" s="3">
         <v>53943000</v>
       </c>
-      <c r="AP76" s="3">
+      <c r="AQ76" s="3">
         <v>53481000</v>
       </c>
     </row>
-    <row r="77" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -8471,257 +8659,266 @@
       <c r="AP77" s="3">
         <v>0</v>
       </c>
+      <c r="AQ77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:43" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E80" s="2">
         <v>46112</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>46022</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45930</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45838</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45747</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45657</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45565</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45473</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45382</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45291</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45199</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45107</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>45016</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44926</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44834</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44742</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44651</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44561</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44469</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44377</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44286</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44196</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>44104</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>44012</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43921</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43830</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43738</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43646</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43555</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43465</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>43373</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>43190</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>43100</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AM80" s="2">
         <v>43008</v>
       </c>
-      <c r="AM80" s="2">
+      <c r="AN80" s="2">
         <v>42916</v>
       </c>
-      <c r="AN80" s="2">
+      <c r="AO80" s="2">
         <v>42825</v>
       </c>
-      <c r="AO80" s="2">
+      <c r="AP80" s="2">
         <v>42735</v>
       </c>
-      <c r="AP80" s="2">
+      <c r="AQ80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>3526000</v>
+      </c>
+      <c r="E81" s="3">
         <v>2174000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>2168000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>3332000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>11123000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>3375000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>4777000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>3629000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>3929000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>3857000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>3260000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>4046000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>4248000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>3834000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>3023000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-4598000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>3396000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>3549000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>3057000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>4035000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>3738000</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>3329000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>3380000</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>2019000</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>2988000</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>2147000</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>3162000</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>3217000</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>3125000</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>3553000</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>2511000</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>2886000</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>3216000</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>3118000</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>14999000</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AM81" s="3">
         <v>2642000</v>
       </c>
-      <c r="AM81" s="3">
+      <c r="AN81" s="3">
         <v>2521000</v>
       </c>
-      <c r="AN81" s="3">
+      <c r="AO81" s="3">
         <v>2573000</v>
       </c>
-      <c r="AO81" s="3">
+      <c r="AP81" s="3">
         <v>2296000</v>
       </c>
-      <c r="AP81" s="3">
+      <c r="AQ81" s="3">
         <v>2237000</v>
       </c>
     </row>
-    <row r="82" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -8764,130 +8961,134 @@
       <c r="AN82" s="3"/>
       <c r="AO82" s="3"/>
       <c r="AP82" s="3"/>
+      <c r="AQ82" s="3"/>
     </row>
-    <row r="83" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>2349000</v>
+      </c>
+      <c r="E83" s="3">
         <v>2231000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>2182000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>2219000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>2154000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>2175000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>2193000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>2202000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>2195000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>2264000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>2199000</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>2150000</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>2162000</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>2213000</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>3472000</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>3333000</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>3468000</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>3548000</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>3582000</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>3477000</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>3383000</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>3362000</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>3252000</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>3320000</v>
-      </c>
-      <c r="AA83" s="3">
-        <v>3264000</v>
       </c>
       <c r="AB83" s="3">
         <v>3264000</v>
       </c>
       <c r="AC83" s="3">
+        <v>3264000</v>
+      </c>
+      <c r="AD83" s="3">
         <v>3177000</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>3180000</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>3276000</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>3320000</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>3197000</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>2477000</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>2403000</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AK83" s="3">
         <v>2599000</v>
       </c>
-      <c r="AK83" s="3">
+      <c r="AL83" s="3">
         <v>2644000</v>
       </c>
-      <c r="AL83" s="3">
+      <c r="AM83" s="3">
         <v>2138000</v>
       </c>
-      <c r="AM83" s="3">
+      <c r="AN83" s="3">
         <v>2541000</v>
       </c>
-      <c r="AN83" s="3">
+      <c r="AO83" s="3">
         <v>2502000</v>
       </c>
-      <c r="AO83" s="3">
+      <c r="AP83" s="3">
         <v>2496000</v>
       </c>
-      <c r="AP83" s="3">
+      <c r="AQ83" s="3">
         <v>2395000</v>
       </c>
     </row>
-    <row r="84" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -9008,8 +9209,11 @@
       <c r="AP84" s="3">
         <v>0</v>
       </c>
+      <c r="AQ84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -9130,8 +9334,11 @@
       <c r="AP85" s="3">
         <v>0</v>
       </c>
+      <c r="AQ85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -9252,8 +9459,11 @@
       <c r="AP86" s="3">
         <v>0</v>
       </c>
+      <c r="AQ86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -9374,8 +9584,11 @@
       <c r="AP87" s="3">
         <v>0</v>
       </c>
+      <c r="AQ87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -9496,130 +9709,136 @@
       <c r="AP88" s="3">
         <v>0</v>
       </c>
+      <c r="AQ88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>8092000</v>
+      </c>
+      <c r="E89" s="3">
         <v>6891000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>8841000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>8693000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>7815000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>8294000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>8080000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>7021000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>4724000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>7848000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>5922000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>8153000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>7198000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>7228000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>5883000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>6946000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>6327000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>7257000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>7689000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>6100000</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>7606000</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>7751000</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>5042000</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>5228000</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>8643000</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>5824000</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>6235000</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>5191000</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>7040000</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>7231000</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>5790000</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>5970000</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>7063000</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>5474000</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>5442000</v>
       </c>
-      <c r="AL89" s="3">
+      <c r="AM89" s="3">
         <v>5147000</v>
       </c>
-      <c r="AM89" s="3">
+      <c r="AN89" s="3">
         <v>5158000</v>
       </c>
-      <c r="AN89" s="3">
+      <c r="AO89" s="3">
         <v>5656000</v>
       </c>
-      <c r="AO89" s="3">
+      <c r="AP89" s="3">
         <v>5743000</v>
       </c>
-      <c r="AP89" s="3">
+      <c r="AQ89" s="3">
         <v>3703000</v>
       </c>
     </row>
-    <row r="90" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -9662,130 +9881,134 @@
       <c r="AN90" s="3"/>
       <c r="AO90" s="3"/>
       <c r="AP90" s="3"/>
+      <c r="AQ90" s="3"/>
     </row>
-    <row r="91" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-2902000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-2351000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-3757000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-3071000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-2679000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-2254000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-3919000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-2915000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-2725000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-2738000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-3338000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-3310000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-2980000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-2751000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-4553000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-3561000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-3156000</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-2497000</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-3905000</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-2866000</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-2144000</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-1859000</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-2835000</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-2387000</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-2076000</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-1881000</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-3087000</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-2511000</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-2263000</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-2092000</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-3167000</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-2384000</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-2250000</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-1973000</v>
       </c>
-      <c r="AK91" s="3">
+      <c r="AL91" s="3">
         <v>-2711000</v>
       </c>
-      <c r="AL91" s="3">
+      <c r="AM91" s="3">
         <v>-2434000</v>
       </c>
-      <c r="AM91" s="3">
+      <c r="AN91" s="3">
         <v>-2327000</v>
       </c>
-      <c r="AN91" s="3">
+      <c r="AO91" s="3">
         <v>-4957000</v>
       </c>
-      <c r="AO91" s="3">
+      <c r="AP91" s="3">
         <v>-3096000</v>
       </c>
-      <c r="AP91" s="3">
+      <c r="AQ91" s="3">
         <v>2061000</v>
       </c>
     </row>
-    <row r="92" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9906,8 +10129,11 @@
       <c r="AP92" s="3">
         <v>0</v>
       </c>
+      <c r="AQ92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -10028,130 +10254,136 @@
       <c r="AP93" s="3">
         <v>0</v>
       </c>
+      <c r="AQ93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-3572000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-2919000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-4437000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-3817000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-4945000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-2958000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-5111000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-3680000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-3368000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-3511000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>4557000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-4190000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-4158000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-3370000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-3982000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-3366000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-4195000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-2597000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-5040000</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-2775000</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-3019000</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-2612000</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-4074000</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-3495000</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-1377000</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-3101000</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-3929000</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-3498000</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-4188000</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-3226000</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-42264000</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-3284000</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-3014000</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-2292000</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3">
         <v>-3610000</v>
       </c>
-      <c r="AL94" s="3">
+      <c r="AM94" s="3">
         <v>-2516000</v>
       </c>
-      <c r="AM94" s="3">
+      <c r="AN94" s="3">
         <v>-3654000</v>
       </c>
-      <c r="AN94" s="3">
+      <c r="AO94" s="3">
         <v>-3753000</v>
       </c>
-      <c r="AO94" s="3">
+      <c r="AP94" s="3">
         <v>-4233000</v>
       </c>
-      <c r="AP94" s="3">
+      <c r="AQ94" s="3">
         <v>-8324000</v>
       </c>
     </row>
-    <row r="95" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -10194,130 +10426,134 @@
       <c r="AN95" s="3"/>
       <c r="AO95" s="3"/>
       <c r="AP95" s="3"/>
+      <c r="AQ95" s="3"/>
     </row>
-    <row r="96" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>1184000</v>
+      </c>
+      <c r="E96" s="3">
         <v>1248000</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>1209000</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>1223000</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>1238000</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>1224000</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>1190000</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>1206000</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>1225000</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>1193000</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>1180000</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>1199000</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>1213000</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>1174000</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-1170000</v>
       </c>
-      <c r="R96" s="3">
+      <c r="S96" s="3">
         <v>-1194000</v>
       </c>
-      <c r="S96" s="3">
+      <c r="T96" s="3">
         <v>-1211000</v>
       </c>
-      <c r="T96" s="3">
+      <c r="U96" s="3">
         <v>-1166000</v>
       </c>
-      <c r="U96" s="3">
+      <c r="V96" s="3">
         <v>-1145000</v>
       </c>
-      <c r="V96" s="3">
+      <c r="W96" s="3">
         <v>-1157000</v>
       </c>
-      <c r="W96" s="3">
+      <c r="X96" s="3">
         <v>-1150000</v>
       </c>
-      <c r="X96" s="3">
+      <c r="Y96" s="3">
         <v>-1080000</v>
       </c>
-      <c r="Y96" s="3">
+      <c r="Z96" s="3">
         <v>-1054000</v>
       </c>
-      <c r="Z96" s="3">
+      <c r="AA96" s="3">
         <v>-1058000</v>
       </c>
-      <c r="AA96" s="3">
+      <c r="AB96" s="3">
         <v>-1051000</v>
       </c>
-      <c r="AB96" s="3">
+      <c r="AC96" s="3">
         <v>-977000</v>
       </c>
-      <c r="AC96" s="3">
+      <c r="AD96" s="3">
         <v>-957000</v>
       </c>
-      <c r="AD96" s="3">
+      <c r="AE96" s="3">
         <v>-955000</v>
       </c>
-      <c r="AE96" s="3">
+      <c r="AF96" s="3">
         <v>-954000</v>
       </c>
-      <c r="AF96" s="3">
+      <c r="AG96" s="3">
         <v>-869000</v>
       </c>
-      <c r="AG96" s="3">
+      <c r="AH96" s="3">
         <v>-865000</v>
       </c>
-      <c r="AH96" s="3">
+      <c r="AI96" s="3">
         <v>-871000</v>
       </c>
-      <c r="AI96" s="3">
+      <c r="AJ96" s="3">
         <v>-878000</v>
       </c>
-      <c r="AJ96" s="3">
+      <c r="AK96" s="3">
         <v>-738000</v>
       </c>
-      <c r="AK96" s="3">
+      <c r="AL96" s="3">
         <v>-736000</v>
       </c>
-      <c r="AL96" s="3">
+      <c r="AM96" s="3">
         <v>-743000</v>
       </c>
-      <c r="AM96" s="3">
+      <c r="AN96" s="3">
         <v>-747000</v>
-      </c>
-      <c r="AN96" s="3">
-        <v>-657000</v>
       </c>
       <c r="AO96" s="3">
         <v>-657000</v>
       </c>
       <c r="AP96" s="3">
+        <v>-657000</v>
+      </c>
+      <c r="AQ96" s="3">
         <v>-663000</v>
       </c>
     </row>
-    <row r="97" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -10438,8 +10674,11 @@
       <c r="AP97" s="3">
         <v>0</v>
       </c>
+      <c r="AQ97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -10560,8 +10799,11 @@
       <c r="AP98" s="3">
         <v>0</v>
       </c>
+      <c r="AQ98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -10682,222 +10924,228 @@
       <c r="AP99" s="3">
         <v>0</v>
       </c>
+      <c r="AQ99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-6305000</v>
+      </c>
+      <c r="E100" s="3">
         <v>-5008000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-3222000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-5243000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-1806000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-4075000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-4424000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-642000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-1794000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-4023000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-10714000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-4644000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-1410000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-3082000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-2885000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-4663000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-4146000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-4490000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-5672000</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-3882000</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-7166000</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-1898000</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-2922000</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-2066000</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-1899000</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>374000</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-355000</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-2094000</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-2407000</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-4325000</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>26006000</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>6094000</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>-4384000</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>-576000</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>-2451000</v>
       </c>
-      <c r="AL100" s="3">
+      <c r="AM100" s="3">
         <v>-1186000</v>
       </c>
-      <c r="AM100" s="3">
+      <c r="AN100" s="3">
         <v>-2794000</v>
       </c>
-      <c r="AN100" s="3">
+      <c r="AO100" s="3">
         <v>-1141000</v>
       </c>
-      <c r="AO100" s="3">
+      <c r="AP100" s="3">
         <v>-1016000</v>
       </c>
-      <c r="AP100" s="3">
+      <c r="AQ100" s="3">
         <v>2352000</v>
       </c>
     </row>
-    <row r="101" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>32000</v>
+      </c>
+      <c r="E101" s="3">
         <v>14000</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-47000</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>38000</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-7000</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-10000</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>27000</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-32000</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-6000</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>20000</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>36000</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-46000</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-41000</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-35000</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>36000</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-46000</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>-41000</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>-35000</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>-56000</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>-3000</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>21000</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>-33000</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>-15000</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>94000</v>
       </c>
-      <c r="AA101" s="3">
-        <v>0</v>
-      </c>
       <c r="AB101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC101" s="3">
         <v>-77000</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>36000</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>-16000</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>-23000</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>8000</v>
-      </c>
-      <c r="AG101" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AH101" s="3" t="s">
         <v>8</v>
@@ -10905,8 +11153,8 @@
       <c r="AI101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AJ101" s="3">
-        <v>0</v>
+      <c r="AJ101" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AK101" s="3">
         <v>0</v>
@@ -10926,126 +11174,132 @@
       <c r="AP101" s="3">
         <v>0</v>
       </c>
+      <c r="AQ101" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="102" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-1783000</v>
+      </c>
+      <c r="E102" s="3">
         <v>-1042000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>1189000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-378000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>1096000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>1275000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-1502000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>2737000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-445000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>304000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-208000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-713000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>1624000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>796000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-948000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-1129000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-2055000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>135000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-3079000</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-560000</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-2558000</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>3208000</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-1969000</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-239000</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>5367000</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>3020000</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>1987000</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-417000</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>422000</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-312000</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>-10713000</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>8780000</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>-335000</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>2606000</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>-657000</v>
       </c>
-      <c r="AL102" s="3">
+      <c r="AM102" s="3">
         <v>1406000</v>
       </c>
-      <c r="AM102" s="3">
+      <c r="AN102" s="3">
         <v>-1324000</v>
       </c>
-      <c r="AN102" s="3">
+      <c r="AO102" s="3">
         <v>731000</v>
       </c>
-      <c r="AO102" s="3">
+      <c r="AP102" s="3">
         <v>494000</v>
       </c>
-      <c r="AP102" s="3">
+      <c r="AQ102" s="3">
         <v>-1858000</v>
       </c>
     </row>
